--- a/Class-exercise/Ex2A_events_normalized.xlsx
+++ b/Class-exercise/Ex2A_events_normalized.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Student\Documents\DataAnalytics\week-02\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Student\Documents\DataAnalytics\Class-exercise\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{637BAFE0-555B-4641-A171-81C219AE3C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF258FDF-64EC-4505-A323-210D198979F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5091876E-AF08-41C4-B976-D2AB9D8B455C}"/>
   </bookViews>
@@ -1307,8 +1307,8 @@
   <cols>
     <col min="1" max="1" width="19.6328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.1796875" customWidth="1"/>
+    <col min="4" max="4" width="13.7265625" customWidth="1"/>
     <col min="5" max="5" width="13.54296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.26953125" customWidth="1"/>
     <col min="7" max="7" width="15.1796875" bestFit="1" customWidth="1"/>
@@ -2575,6 +2575,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ced60a7f-99b1-48d2-b555-34851c8026ae" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9e0b35a9-e6cb-436b-81d4-4440ba439ca5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CA5D0A6329BB324E86983B32928CFC2E" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3d7eac4bce3bbb09c82bd908806be82e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9e0b35a9-e6cb-436b-81d4-4440ba439ca5" xmlns:ns3="ced60a7f-99b1-48d2-b555-34851c8026ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="eb51570e5b7cb8bd524bc2df5324d4a3" ns2:_="" ns3:_="">
     <xsd:import namespace="9e0b35a9-e6cb-436b-81d4-4440ba439ca5"/>
@@ -2815,17 +2826,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ced60a7f-99b1-48d2-b555-34851c8026ae" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9e0b35a9-e6cb-436b-81d4-4440ba439ca5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D48FB9E6-6DE3-40FB-81F7-677295638F7C}">
   <ds:schemaRefs>
@@ -2835,6 +2835,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EE6EC55-B0E7-4ACE-A5DA-E03DCA4973DE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ced60a7f-99b1-48d2-b555-34851c8026ae"/>
+    <ds:schemaRef ds:uri="9e0b35a9-e6cb-436b-81d4-4440ba439ca5"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6414E68-BBC1-4A96-B078-EF7EE95D29CE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2851,15 +2862,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EE6EC55-B0E7-4ACE-A5DA-E03DCA4973DE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ced60a7f-99b1-48d2-b555-34851c8026ae"/>
-    <ds:schemaRef ds:uri="9e0b35a9-e6cb-436b-81d4-4440ba439ca5"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>